--- a/code_mapping/[iCUBE] 6. 회계기수매핑정의서.xlsx
+++ b/code_mapping/[iCUBE] 6. 회계기수매핑정의서.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qkang\OneDrive\바탕 화면\migraion\01. 템플릿\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qkang\OneDrive\바탕 화면\migraion\01. 템플릿\통합\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
   <si>
     <t>SOURCE 회사코드</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -74,6 +74,14 @@
   </si>
   <si>
     <t>Y</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>회계기수매핑정의서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260513</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -439,7 +447,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -479,6 +487,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -497,35 +535,112 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -807,180 +922,198 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:F21"/>
+  <dimension ref="B1:F22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.125" customWidth="1"/>
-    <col min="2" max="6" width="30.625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="2.125" style="50" customWidth="1"/>
+    <col min="2" max="6" width="30.625" style="59" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="22"/>
-    </row>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
+    <row r="1" spans="2:6" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+    </row>
+    <row r="2" spans="2:6" s="31" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="29"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+    </row>
+    <row r="3" spans="2:6" s="31" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="15"/>
-    </row>
-    <row r="3" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="16"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
-    </row>
-    <row r="4" spans="2:6" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="5" t="s">
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="34"/>
+    </row>
+    <row r="4" spans="2:6" s="31" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="35"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="37"/>
+    </row>
+    <row r="5" spans="2:6" s="31" customFormat="1" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="38"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+    </row>
+    <row r="6" spans="2:6" s="31" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C6" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D6" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E6" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F6" s="41" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="1" t="s">
+    <row r="7" spans="2:6" s="31" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C7" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D7" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E7" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F7" s="45" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="23"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="10"/>
-    </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="25"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="11"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="49"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="25"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="11"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="54"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="25"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="11"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="54"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="25"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="11"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="54"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="25"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="11"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="54"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="25"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="11"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="54"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="25"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="11"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="54"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="11"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="54"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="25"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="11"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="54"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="25"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="11"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="54"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="25"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="11"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="53"/>
+      <c r="F18" s="54"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="25"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="11"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="54"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="25"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="11"/>
-    </row>
-    <row r="21" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="27"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="12"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="54"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="51"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="54"/>
+    </row>
+    <row r="22" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="55"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="58"/>
     </row>
   </sheetData>
+  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="1">
-    <mergeCell ref="B2:F3"/>
+    <mergeCell ref="B3:F4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -998,23 +1131,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="22"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="15"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="25"/>
     </row>
     <row r="3" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="16"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="28"/>
     </row>
     <row r="4" spans="2:6" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="9"/>
@@ -1057,16 +1190,16 @@
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="23">
+      <c r="B7" s="17">
         <v>22</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="18">
         <v>1111</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="18">
         <v>20180101</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="14">
         <v>20181231</v>
       </c>
       <c r="F7" s="10" t="s">
@@ -1074,16 +1207,16 @@
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="25">
+      <c r="B8" s="19">
         <v>23</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="20">
         <v>1111</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="20">
         <v>20190101</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="13">
         <v>20191231</v>
       </c>
       <c r="F8" s="11" t="s">
@@ -1091,16 +1224,16 @@
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="25">
+      <c r="B9" s="19">
         <v>24</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="20">
         <v>1111</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="20">
         <v>20200101</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="13">
         <v>20201231</v>
       </c>
       <c r="F9" s="11" t="s">
@@ -1108,16 +1241,16 @@
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="25">
+      <c r="B10" s="19">
         <v>25</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="20">
         <v>1111</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="20">
         <v>20210101</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="13">
         <v>20211231</v>
       </c>
       <c r="F10" s="11" t="s">
@@ -1125,16 +1258,16 @@
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="25">
+      <c r="B11" s="19">
         <v>26</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="20">
         <v>1111</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="20">
         <v>20220101</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="13">
         <v>20221231</v>
       </c>
       <c r="F11" s="11" t="s">
@@ -1142,16 +1275,16 @@
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="25">
+      <c r="B12" s="19">
         <v>27</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="20">
         <v>1111</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="20">
         <v>20230101</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="13">
         <v>20231231</v>
       </c>
       <c r="F12" s="11" t="s">
@@ -1159,69 +1292,70 @@
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="25"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="13"/>
       <c r="F13" s="11"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="25"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="13"/>
       <c r="F14" s="11"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="13"/>
       <c r="F15" s="11"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="25"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="13"/>
       <c r="F16" s="11"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="25"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="13"/>
       <c r="F17" s="11"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="25"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="13"/>
       <c r="F18" s="11"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="25"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="13"/>
       <c r="F19" s="11"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="25"/>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="13"/>
       <c r="F20" s="11"/>
     </row>
     <row r="21" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="27"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="15"/>
       <c r="F21" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="B2:F3"/>
   </mergeCells>

--- a/code_mapping/[iCUBE] 6. 회계기수매핑정의서.xlsx
+++ b/code_mapping/[iCUBE] 6. 회계기수매핑정의서.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qkang\OneDrive\바탕 화면\migraion\01. 템플릿\통합\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="회계기수매핑정의서" sheetId="7" r:id="rId1"/>
@@ -81,7 +81,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20260513</t>
+    <t>20260903</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -517,24 +517,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -543,24 +525,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -641,6 +605,42 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -925,193 +925,193 @@
   <dimension ref="B1:F22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.125" style="50" customWidth="1"/>
-    <col min="2" max="6" width="30.625" style="59" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="50"/>
+    <col min="1" max="1" width="2.125" style="38" customWidth="1"/>
+    <col min="2" max="6" width="30.625" style="47" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="30" t="s">
+    <row r="1" spans="2:6" s="25" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-    </row>
-    <row r="2" spans="2:6" s="31" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="29"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-    </row>
-    <row r="3" spans="2:6" s="31" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="32" t="s">
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+    </row>
+    <row r="2" spans="2:6" s="25" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="23"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+    </row>
+    <row r="3" spans="2:6" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
-    </row>
-    <row r="4" spans="2:6" s="31" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="35"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="37"/>
-    </row>
-    <row r="5" spans="2:6" s="31" customFormat="1" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="38"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-    </row>
-    <row r="6" spans="2:6" s="31" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="39" t="s">
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="50"/>
+    </row>
+    <row r="4" spans="2:6" s="25" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="51"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="53"/>
+    </row>
+    <row r="5" spans="2:6" s="25" customFormat="1" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="26"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+    </row>
+    <row r="6" spans="2:6" s="25" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="29" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:6" s="31" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="42" t="s">
+    <row r="7" spans="2:6" s="25" customFormat="1" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="44" t="s">
+      <c r="E7" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="45" t="s">
+      <c r="F7" s="33" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B8" s="46"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="49"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="37"/>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="51"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="54"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="42"/>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="51"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="54"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="42"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="51"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="54"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="42"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="51"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="54"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="42"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="51"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="54"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="42"/>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="51"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="54"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="42"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="51"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="54"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="42"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="51"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="54"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="42"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="51"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="54"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="42"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="51"/>
-      <c r="C18" s="52"/>
-      <c r="D18" s="52"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="54"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="42"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="51"/>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="54"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="42"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B20" s="51"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="54"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="42"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B21" s="51"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="54"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="42"/>
     </row>
     <row r="22" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="55"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="58"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="44"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="46"/>
     </row>
   </sheetData>
-  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="gIt3YsUYGh1akhOqauBl6AJ+6dQ+FEIaMdyEEEK4yJNfCoxotgUOXUXuXhpmZTdi1LamYk/HhHbm5704kGVNCg==" saltValue="9ESVsz48LphDo2loV39XOQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="B3:F4"/>
   </mergeCells>
@@ -1134,20 +1134,20 @@
       <c r="B1" s="16"/>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="25"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="56"/>
     </row>
     <row r="3" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="26"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="28"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="59"/>
     </row>
     <row r="4" spans="2:6" ht="8.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="9"/>
@@ -1355,7 +1355,7 @@
       <c r="F21" s="12"/>
     </row>
   </sheetData>
-  <sheetProtection password="8396" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="EbSqubhX7mKrGCkXptUtbpsH4ZL0TiZs3P6d9IaFod2DJoFd7tFh+d6N4vG8JvEEg0rVVnShpvqqBKDGsg5meA==" saltValue="oKzpIqka+yz2ie/TCObeCw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="B2:F3"/>
   </mergeCells>
